--- a/results/Int All Data -0.3/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_9_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8720721039254917</v>
+        <v>0.8794769616019766</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8707878021488916</v>
+        <v>0.8807706226627787</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.869180085107091</v>
+        <v>0.8794769616019766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8688510542713693</v>
+        <v>0.8794769616019766</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8694978848017703</v>
+        <v>0.8723749287654481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8714290171087715</v>
+        <v>0.8717131233803239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8717505605171316</v>
+        <v>0.8733395589905284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8717505605171316</v>
+        <v>0.8752837942954124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8733713805568151</v>
+        <v>0.8739976206619717</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8730479652916145</v>
+        <v>0.8730292467232106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8717636635150143</v>
+        <v>0.8730348622937317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8746575541902555</v>
+        <v>0.8727208063127332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.874334138925055</v>
+        <v>0.8730460934347741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8736910521083348</v>
+        <v>0.872724550026414</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8736910521083348</v>
+        <v>0.8739994925188121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8736891802514943</v>
+        <v>0.8765924302109375</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.872724550026414</v>
+        <v>0.8765830709267355</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8704625150268508</v>
+        <v>0.8717748946560566</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8643812681206141</v>
+        <v>0.8724179814727769</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8643812681206141</v>
+        <v>0.873064812003178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8643812681206141</v>
+        <v>0.8733863554115381</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8640653402827752</v>
+        <v>0.8737078988198983</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8650449453625786</v>
+        <v>0.871124320411975</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8627960133608981</v>
+        <v>0.871124320411975</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8615060960137768</v>
+        <v>0.8714477356771755</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8586009741974934</v>
+        <v>0.8727376530242967</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8605283627908138</v>
+        <v>0.8698418904922152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8605283627908138</v>
+        <v>0.8685519731450939</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8640709558532964</v>
+        <v>0.872758243449541</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8618201519947755</v>
+        <v>0.8701690494710964</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8554023868254556</v>
+        <v>0.8682379171640953</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8557239302338158</v>
+        <v>0.8682341734504145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8264859423551287</v>
+        <v>0.8682341734504145</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8358050856270512</v>
+        <v>0.8675910866336942</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.834530143134653</v>
+        <v>0.8682341734504145</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8345282712778126</v>
+        <v>0.867910758185214</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8371193371130976</v>
+        <v>0.8672714150821745</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8377624239298178</v>
+        <v>0.8653683606277791</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8348685332545767</v>
+        <v>0.8653683606277791</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8329392728044158</v>
+        <v>0.8660039600171379</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8294022953124545</v>
+        <v>0.8644018585458584</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8399963810767752</v>
+        <v>0.8644018585458584</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8277833471296115</v>
+        <v>0.8618295112789773</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8300772036954613</v>
+        <v>0.8566792011746942</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8233304076904198</v>
+        <v>0.861162090323332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8233304076904198</v>
+        <v>0.8669274093917296</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8095096567014555</v>
+        <v>0.8562865272063993</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7480929938478305</v>
+        <v>0.8588719774711631</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7477658348689492</v>
+        <v>0.8591953927363636</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7361977595953462</v>
+        <v>0.8591953927363636</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7355565446354664</v>
+        <v>0.858838284048036</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7333057407769454</v>
+        <v>0.8553050502697553</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7104817743538974</v>
+        <v>0.8559387778022737</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7101864369413027</v>
+        <v>0.8578792693934767</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7105098522065032</v>
+        <v>0.8604665915150809</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7205039038614327</v>
+        <v>0.8678808084757678</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7233809478251103</v>
+        <v>0.8698100689259285</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7131084054691497</v>
+        <v>0.8662656040066056</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7105360582022686</v>
+        <v>0.866276835147648</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6989417769329002</v>
+        <v>0.865338410918333</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7063653531777889</v>
+        <v>0.865338410918333</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6915781001069039</v>
+        <v>0.848290994704725</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6703581070119757</v>
+        <v>0.8518317159103672</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6671426729283744</v>
+        <v>0.8518317159103672</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6639384699858155</v>
+        <v>0.85478176229082</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6697187639089363</v>
+        <v>0.859619888270945</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6096107369708365</v>
+        <v>0.8576962433913055</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6047632517065095</v>
+        <v>0.8564100697578649</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6108519860401076</v>
+        <v>0.8467225866565725</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6101901806549835</v>
+        <v>0.8441614705307339</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6096051214003153</v>
+        <v>0.8444773983685727</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6176418347524781</v>
+        <v>0.8448008136337732</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6137945449931989</v>
+        <v>0.8415741484091297</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6472069816100464</v>
+        <v>0.8367416379995258</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6285593357819994</v>
+        <v>0.8419144103858938</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6343527327030029</v>
+        <v>0.8457617001451729</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6324309596802037</v>
+        <v>0.8255512618394945</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6379046850496874</v>
+        <v>0.825543774412133</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6369381829677666</v>
+        <v>0.8252259747174535</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6369381829677666</v>
+        <v>0.822952708576848</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6366147677025661</v>
+        <v>0.8226517555937322</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6301838995353636</v>
+        <v>0.8120464386883691</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5922473929193894</v>
+        <v>0.8117248952800089</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5890338306926286</v>
+        <v>0.8088328764616082</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5797128155638657</v>
+        <v>0.8075541902555292</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5861324525900259</v>
+        <v>0.808836620175289</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5755346231120244</v>
+        <v>0.808836620175289</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5723191890284232</v>
+        <v>0.8088384920321294</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5954478521482677</v>
+        <v>0.7783424083726076</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5935129761275857</v>
+        <v>0.7889159037116842</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5957469332745432</v>
+        <v>0.7902058210588054</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5674586007662135</v>
+        <v>0.7853789262197227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5741698314912875</v>
+        <v>0.7397361929759612</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5638916735648057</v>
+        <v>0.735208379263154</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5777142964106106</v>
+        <v>0.7316732736280329</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5703131824478064</v>
+        <v>0.7121882838400519</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5741735752049684</v>
+        <v>0.7223896956360778</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5748241494490501</v>
+        <v>0.6904483305116824</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5748297650195713</v>
+        <v>0.6904483305116824</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.588628053726451</v>
+        <v>0.6715278095531254</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.59375777340549</v>
+        <v>0.6696958856586648</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.589590812094691</v>
+        <v>0.6716214023951448</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5734612296851537</v>
+        <v>0.6793609064778726</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.572825630295795</v>
+        <v>0.6841372611822648</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5590123667341922</v>
+        <v>0.6831501686750998</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5561166042021106</v>
+        <v>0.6930300370627654</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5483602534078194</v>
+        <v>0.6920710224082063</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5483602534078194</v>
+        <v>0.6509078505675886</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5486817968161795</v>
+        <v>0.4424524652354588</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5636988723102457</v>
+        <v>0.4563986306327292</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5579148346734442</v>
+        <v>0.4840438763243387</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.537351031393119</v>
+        <v>0.48538183799703</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.537351031393119</v>
+        <v>0.486028668527431</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.537351031393119</v>
+        <v>0.4722041738247859</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5383643298960495</v>
+        <v>0.4587457311264834</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5209803954193584</v>
+        <v>0.4629351547193671</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5087654896153542</v>
+        <v>0.4557825817481479</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5204346451583383</v>
+        <v>0.4551394949314277</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5151813829278337</v>
+        <v>0.4515781833005412</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5174415460705565</v>
+        <v>0.45542360120298</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5171237463758772</v>
+        <v>0.4226392765481296</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4823727241340582</v>
+        <v>0.4414460302076097</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4699519140776113</v>
+        <v>0.5001957130318674</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4702790730564926</v>
+        <v>0.5025644438713327</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4790880313473626</v>
+        <v>0.5112423721833754</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4525062083251873</v>
+        <v>0.5141325191449357</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4459911066001672</v>
+        <v>0.5141325191449357</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5244967824860755</v>
+        <v>0.5261213462394396</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5122987233936348</v>
+        <v>0.5455936489977247</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5126221386588353</v>
+        <v>0.5398283299293271</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5077896282492315</v>
+        <v>0.5549109204128069</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5084420743501536</v>
+        <v>0.5163837389716435</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5087654896153542</v>
+        <v>0.5080385852090032</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5087654896153542</v>
+        <v>0.507717041800643</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5090889048805547</v>
+        <v>0.5112521474357641</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5149141233678448</v>
+        <v>0.5112521474357641</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5165330715506878</v>
+        <v>0.5125364492123642</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5061613207821866</v>
+        <v>0.5067505397187223</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5094085764320745</v>
+        <v>0.5070739549839228</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5094085764320745</v>
+        <v>0.5064140214556391</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.510958265911823</v>
+        <v>0.5089863687225201</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5047085518899515</v>
+        <v>0.5105922139074803</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5167235849802208</v>
+        <v>0.5118802593977613</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4854309222430668</v>
+        <v>0.513162689317521</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4906186694841579</v>
+        <v>0.513162689317521</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4887549240234107</v>
+        <v>0.512846761479682</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5043574747403319</v>
+        <v>0.5096257118255596</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5079000678028145</v>
+        <v>0.5138039042774009</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4958719317146625</v>
+        <v>0.5032098185130801</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4961916032661822</v>
+        <v>0.5025667316963599</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.488900928856961</v>
+        <v>0.5028864032478796</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4892224722653212</v>
+        <v>0.4996765847347995</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4892224722653212</v>
+        <v>0.4996765847347995</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4856780073459981</v>
+        <v>0.4996765847347995</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4943915009380083</v>
+        <v>0.4996765847347995</v>
       </c>
     </row>
   </sheetData>
